--- a/book/model/build/Ch39_skeleton.xlsx
+++ b/book/model/build/Ch39_skeleton.xlsx
@@ -719,7 +719,7 @@
     <row r="31">
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Build-along file Ch39_skeleton.xlsx: the companion model at the end of Chapter 39 (u09 Section 0.4 rows of Chapters 39 to 39; model version 1.4).</t>
+          <t>Build-along file Ch39_skeleton.xlsx: the companion model at the end of Chapter 39 (u09 Section 0.4 rows of Chapters 39 to 39; model version 1.5).</t>
         </is>
       </c>
     </row>
